--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-23).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-23).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>R$ 4.182,57</t>
-  </si>
-  <si>
-    <t>46.2</t>
-  </si>
-  <si>
-    <t>28.6</t>
-  </si>
-  <si>
-    <t>4.88</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 4.187,86</t>
+  </si>
+  <si>
+    <t>46.3</t>
+  </si>
+  <si>
+    <t>28.7</t>
+  </si>
+  <si>
+    <t>4.89</t>
   </si>
   <si>
     <t>18.7</t>
@@ -956,13 +956,13 @@
     <t>7.0</t>
   </si>
   <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>46.7%</t>
-  </si>
-  <si>
-    <t>18.7%</t>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>46.1%</t>
+  </si>
+  <si>
+    <t>18.6%</t>
   </si>
   <si>
     <t>1.6%</t>
@@ -974,7 +974,7 @@
     <t>4.7%</t>
   </si>
   <si>
-    <t>1.4%</t>
+    <t>1.3%</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -989,19 +989,19 @@
     <t>4.3%</t>
   </si>
   <si>
-    <t>1162.0</t>
-  </si>
-  <si>
-    <t>940.0</t>
-  </si>
-  <si>
-    <t>83.0</t>
+    <t>1198.0</t>
+  </si>
+  <si>
+    <t>971.0</t>
+  </si>
+  <si>
+    <t>85.0</t>
   </si>
   <si>
     <t>22.0</t>
   </si>
   <si>
-    <t>238.0</t>
+    <t>244.0</t>
   </si>
   <si>
     <t>70.0</t>
@@ -1010,13 +1010,13 @@
     <t>16.0</t>
   </si>
   <si>
-    <t>356.0</t>
-  </si>
-  <si>
-    <t>153.0</t>
-  </si>
-  <si>
-    <t>216.0</t>
+    <t>371.0</t>
+  </si>
+  <si>
+    <t>156.0</t>
+  </si>
+  <si>
+    <t>226.0</t>
   </si>
   <si>
     <t>0.6%</t>
@@ -3242,7 +3242,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3272,35 +3272,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>6863.7600000000002</v>
+      </c>
+      <c r="N13" s="6">
+        <v>75</v>
+      </c>
+      <c r="O13" s="6">
+        <v>55</v>
+      </c>
+      <c r="P13" s="7">
+        <v>6.1448202702702703</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>19.405454545454546</v>
+      </c>
+      <c r="R13" s="8">
+        <v>6.6303036363636361</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.30909090909090908</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.072727272727272724</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -7609,7 +7667,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7639,35 +7697,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>2882.3099999999999</v>
+      </c>
+      <c r="N42" s="6">
+        <v>36</v>
+      </c>
+      <c r="O42" s="6">
+        <v>24</v>
+      </c>
+      <c r="P42" s="7">
+        <v>4.3122558823529413</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>14.653470833333332</v>
+      </c>
+      <c r="R42" s="8">
+        <v>3.2717391304347827</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -9057,7 +9173,7 @@
         <v>19606</v>
       </c>
       <c r="B52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C52" s="4">
         <v>51</v>
@@ -9087,35 +9203,93 @@
         <v>58</v>
       </c>
       <c r="L52" s="4"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="6"/>
-      <c r="O52" s="6"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="8"/>
-      <c r="R52" s="8"/>
-      <c r="S52" s="8"/>
-      <c r="T52" s="9"/>
-      <c r="U52" s="9"/>
-      <c r="V52" s="9"/>
-      <c r="W52" s="9"/>
-      <c r="X52" s="9"/>
-      <c r="Y52" s="9"/>
-      <c r="Z52" s="9"/>
-      <c r="AA52" s="9"/>
-      <c r="AB52" s="9"/>
-      <c r="AC52" s="9"/>
-      <c r="AD52" s="6"/>
-      <c r="AE52" s="6"/>
-      <c r="AF52" s="6"/>
-      <c r="AG52" s="6"/>
-      <c r="AH52" s="6"/>
-      <c r="AI52" s="6"/>
-      <c r="AJ52" s="6"/>
-      <c r="AK52" s="6"/>
-      <c r="AL52" s="6"/>
-      <c r="AM52" s="6"/>
-      <c r="AN52" s="9"/>
-      <c r="AO52" s="6"/>
+      <c r="M52" s="5">
+        <v>4573.1000000000004</v>
+      </c>
+      <c r="N52" s="6">
+        <v>44</v>
+      </c>
+      <c r="O52" s="6">
+        <v>18</v>
+      </c>
+      <c r="P52" s="7">
+        <v>6.9405804347826088</v>
+      </c>
+      <c r="Q52" s="8">
+        <v>16.341666666666665</v>
+      </c>
+      <c r="R52" s="8">
+        <v>2.8858999999999999</v>
+      </c>
+      <c r="S52" s="8">
+        <v>8</v>
+      </c>
+      <c r="T52" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="U52" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V52" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="W52" s="9">
+        <v>0</v>
+      </c>
+      <c r="X52" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AB52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE52" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF52" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP52" s="4">
         <v>58</v>
       </c>
@@ -9190,7 +9364,9 @@
       <c r="N53" s="6">
         <v>42</v>
       </c>
-      <c r="O53" s="6"/>
+      <c r="O53" s="6">
+        <v>31</v>
+      </c>
       <c r="P53" s="7">
         <v>3.3841261904761901</v>
       </c>
@@ -9200,31 +9376,75 @@
       <c r="R53" s="8">
         <v>3.2526870967741934</v>
       </c>
-      <c r="S53" s="8"/>
+      <c r="S53" s="8">
+        <v>7</v>
+      </c>
       <c r="T53" s="9">
         <v>0.64516129032258063</v>
       </c>
-      <c r="U53" s="9"/>
-      <c r="V53" s="9"/>
-      <c r="W53" s="9"/>
-      <c r="X53" s="9"/>
-      <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
-      <c r="AA53" s="9"/>
-      <c r="AB53" s="9"/>
-      <c r="AC53" s="9"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="6"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="6"/>
-      <c r="AL53" s="6"/>
-      <c r="AM53" s="6"/>
-      <c r="AN53" s="9"/>
-      <c r="AO53" s="6"/>
+      <c r="U53" s="9">
+        <v>0</v>
+      </c>
+      <c r="V53" s="9">
+        <v>0</v>
+      </c>
+      <c r="W53" s="9">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP53" s="4">
         <v>58</v>
       </c>
@@ -9891,7 +10111,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -9921,18 +10141,30 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>4574.1499999999996</v>
+      </c>
+      <c r="N58" s="6">
+        <v>56</v>
+      </c>
       <c r="O58" s="6">
         <v>41</v>
       </c>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>2.974405357142857</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>17.039024390243902</v>
+      </c>
+      <c r="R58" s="8">
+        <v>7.2299999999999995</v>
+      </c>
       <c r="S58" s="8">
         <v>7</v>
       </c>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.3902439024390244</v>
+      </c>
       <c r="U58" s="9">
         <v>0.073170731707317069</v>
       </c>
@@ -11695,7 +11927,7 @@
         <v>19648</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C70" s="4">
         <v>51</v>
@@ -11725,18 +11957,30 @@
         <v>58</v>
       </c>
       <c r="L70" s="4"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="6"/>
+      <c r="M70" s="5">
+        <v>3936.3499999999999</v>
+      </c>
+      <c r="N70" s="6">
+        <v>48</v>
+      </c>
       <c r="O70" s="6">
         <v>21</v>
       </c>
-      <c r="P70" s="7"/>
-      <c r="Q70" s="8"/>
-      <c r="R70" s="8"/>
+      <c r="P70" s="7">
+        <v>3.134313725490196</v>
+      </c>
+      <c r="Q70" s="8">
+        <v>20.331747619047619</v>
+      </c>
+      <c r="R70" s="8">
+        <v>10.778335</v>
+      </c>
       <c r="S70" s="8">
         <v>7</v>
       </c>
-      <c r="T70" s="9"/>
+      <c r="T70" s="9">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="U70" s="9">
         <v>0.23809523809523808</v>
       </c>
@@ -12593,7 +12837,9 @@
       <c r="N76" s="6">
         <v>79</v>
       </c>
-      <c r="O76" s="6"/>
+      <c r="O76" s="6">
+        <v>45</v>
+      </c>
       <c r="P76" s="7">
         <v>2.9339426829268294</v>
       </c>
@@ -12603,31 +12849,75 @@
       <c r="R76" s="8">
         <v>7.7333325581395345</v>
       </c>
-      <c r="S76" s="8"/>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
       <c r="T76" s="9">
         <v>0.33333333333333331</v>
       </c>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="U76" s="9">
+        <v>0.35555555555555557</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.088888888888888892</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.15555555555555556</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.044444444444444446</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>19</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -25106,7 +25396,7 @@
         <v>19868</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C161" s="4">
         <v>51</v>
@@ -25136,10 +25426,16 @@
         <v>58</v>
       </c>
       <c r="L161" s="4"/>
-      <c r="M161" s="5"/>
-      <c r="N161" s="6"/>
+      <c r="M161" s="5">
+        <v>3240.5999999999999</v>
+      </c>
+      <c r="N161" s="6">
+        <v>41</v>
+      </c>
       <c r="O161" s="6"/>
-      <c r="P161" s="7"/>
+      <c r="P161" s="7">
+        <v>7.9070824999999996</v>
+      </c>
       <c r="Q161" s="8"/>
       <c r="R161" s="8"/>
       <c r="S161" s="8"/>
@@ -27846,7 +28142,9 @@
       <c r="N179" s="6">
         <v>56</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>23</v>
+      </c>
       <c r="P179" s="7">
         <v>3.8938277777777777</v>
       </c>
@@ -27856,31 +28154,75 @@
       <c r="R179" s="8">
         <v>3.2804347826086957</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.78260869565217395</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-23).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-23).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>30</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 4.187,86</t>
+    <t>R$ 4.173,50</t>
   </si>
   <si>
-    <t>46.3</t>
+    <t>45.9</t>
   </si>
   <si>
-    <t>28.7</t>
+    <t>28.6</t>
   </si>
   <si>
-    <t>4.89</t>
+    <t>4.93</t>
   </si>
   <si>
-    <t>18.7</t>
+    <t>18.8</t>
   </si>
   <si>
-    <t>7.0</t>
+    <t>7.1</t>
   </si>
   <si>
-    <t>6.1</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>46.1%</t>
+    <t>45.9%</t>
   </si>
   <si>
-    <t>18.6%</t>
+    <t>18.4%</t>
   </si>
   <si>
     <t>1.6%</t>
@@ -971,7 +971,7 @@
     <t>0.4%</t>
   </si>
   <si>
-    <t>4.7%</t>
+    <t>4.6%</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -986,34 +986,34 @@
     <t>3.0%</t>
   </si>
   <si>
-    <t>4.3%</t>
+    <t>4.2%</t>
   </si>
   <si>
-    <t>1198.0</t>
+    <t>1227.0</t>
   </si>
   <si>
-    <t>971.0</t>
+    <t>994.0</t>
   </si>
   <si>
-    <t>85.0</t>
+    <t>86.0</t>
   </si>
   <si>
     <t>22.0</t>
   </si>
   <si>
-    <t>244.0</t>
+    <t>251.0</t>
   </si>
   <si>
-    <t>70.0</t>
+    <t>72.0</t>
   </si>
   <si>
-    <t>16.0</t>
+    <t>18.0</t>
   </si>
   <si>
-    <t>371.0</t>
+    <t>383.0</t>
   </si>
   <si>
-    <t>156.0</t>
+    <t>161.0</t>
   </si>
   <si>
     <t>226.0</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>7474.5100000000002</v>
+      </c>
+      <c r="N6" s="6">
+        <v>86</v>
+      </c>
+      <c r="O6" s="6">
+        <v>70</v>
+      </c>
+      <c r="P6" s="7">
+        <v>5.5686987804878054</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>14.55857142857143</v>
+      </c>
+      <c r="R6" s="8">
+        <v>1.7292857142857143</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.042857142857142858</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -4961,7 +5019,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4991,14 +5049,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>5250.1800000000003</v>
+      </c>
+      <c r="N24" s="6">
+        <v>57</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>4.2703036363636366</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>23.871030952380952</v>
+      </c>
+      <c r="R24" s="8">
+        <v>12.457935714285714</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.14285714285714285</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6785,7 +6855,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6815,35 +6885,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>3046.7600000000002</v>
+      </c>
+      <c r="N36" s="6">
+        <v>31</v>
+      </c>
+      <c r="O36" s="6">
+        <v>17</v>
+      </c>
+      <c r="P36" s="7">
+        <v>4.4649413793103454</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>24.921570588235294</v>
+      </c>
+      <c r="R36" s="8">
+        <v>16.85952142857143</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.35294117647058826</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7088,7 +7216,7 @@
         <v>3.5429499999999998</v>
       </c>
       <c r="S38" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" s="9">
         <v>0.46153846153846156</v>
@@ -9074,7 +9202,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9104,35 +9232,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>1282.3800000000001</v>
+      </c>
+      <c r="N51" s="6">
+        <v>12</v>
+      </c>
+      <c r="O51" s="6">
+        <v>6</v>
+      </c>
+      <c r="P51" s="7">
+        <v>5.5972250000000008</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>29.736116666666664</v>
+      </c>
+      <c r="R51" s="8">
+        <v>19.880000000000003</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U51" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -14776,7 +14962,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14804,14 +14990,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>4362.6999999999998</v>
+      </c>
+      <c r="N89" s="6">
+        <v>45</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>7.3602272727272728</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>28.053333333333335</v>
+      </c>
+      <c r="R89" s="8">
+        <v>10.104446666666666</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.066666666666666666</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -16689,7 +16887,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16719,35 +16917,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>3367.9000000000001</v>
+      </c>
+      <c r="N102" s="6">
+        <v>38</v>
+      </c>
+      <c r="O102" s="6">
+        <v>29</v>
+      </c>
+      <c r="P102" s="7">
+        <v>7.6978078947368429</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>20.633906896551721</v>
+      </c>
+      <c r="R102" s="8">
+        <v>6.9993320000000008</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.13793103448275862</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -24989,7 +25245,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25019,35 +25275,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>1787.5</v>
+      </c>
+      <c r="N158" s="6">
+        <v>18</v>
+      </c>
+      <c r="O158" s="6">
+        <v>15</v>
+      </c>
+      <c r="P158" s="7">
+        <v>4.7240722222222225</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>14.17</v>
+      </c>
+      <c r="R158" s="8">
+        <v>2.3966666666666669</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -30592,7 +30906,9 @@
       <c r="N195" s="6">
         <v>49</v>
       </c>
-      <c r="O195" s="6"/>
+      <c r="O195" s="6">
+        <v>35</v>
+      </c>
       <c r="P195" s="7">
         <v>6.4958333333333336</v>
       </c>
@@ -30602,31 +30918,75 @@
       <c r="R195" s="8">
         <v>7.855714285714285</v>
       </c>
-      <c r="S195" s="8"/>
+      <c r="S195" s="8">
+        <v>7</v>
+      </c>
       <c r="T195" s="9">
         <v>0.20000000000000001</v>
       </c>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
-      <c r="W195" s="9"/>
-      <c r="X195" s="9"/>
-      <c r="Y195" s="9"/>
-      <c r="Z195" s="9"/>
-      <c r="AA195" s="9"/>
-      <c r="AB195" s="9"/>
-      <c r="AC195" s="9"/>
-      <c r="AD195" s="6"/>
-      <c r="AE195" s="6"/>
-      <c r="AF195" s="6"/>
-      <c r="AG195" s="6"/>
-      <c r="AH195" s="6"/>
-      <c r="AI195" s="6"/>
-      <c r="AJ195" s="6"/>
-      <c r="AK195" s="6"/>
-      <c r="AL195" s="6"/>
-      <c r="AM195" s="6"/>
-      <c r="AN195" s="9"/>
-      <c r="AO195" s="6"/>
+      <c r="U195" s="9">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="V195" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="W195" s="9">
+        <v>0</v>
+      </c>
+      <c r="X195" s="9">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="Y195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD195" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH195" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO195" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP195" s="4">
         <v>58</v>
       </c>
@@ -32278,7 +32638,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>51</v>
@@ -32308,35 +32668,93 @@
         <v>58</v>
       </c>
       <c r="L207" s="4"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="6"/>
-      <c r="O207" s="6"/>
-      <c r="P207" s="7"/>
-      <c r="Q207" s="8"/>
-      <c r="R207" s="8"/>
-      <c r="S207" s="8"/>
-      <c r="T207" s="9"/>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="M207" s="5">
+        <v>0</v>
+      </c>
+      <c r="N207" s="6">
+        <v>16</v>
+      </c>
+      <c r="O207" s="6">
+        <v>10</v>
+      </c>
+      <c r="P207" s="7">
+        <v>6.7270812500000003</v>
+      </c>
+      <c r="Q207" s="8">
+        <v>20.43</v>
+      </c>
+      <c r="R207" s="8">
+        <v>8.625922222222222</v>
+      </c>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
+      <c r="T207" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="U207" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>
